--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75FEBF3-E57D-4037-BA35-B147AB3B7F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05DD79D-EA08-456F-A3C0-52F8E76719C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="694">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2712,6 +2712,26 @@
   </si>
   <si>
     <t>janjanoo</t>
+  </si>
+  <si>
+    <t>신세계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박쭈이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fidfidfid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>신세계</t>
@@ -3097,7 +3117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A2A291-B3BF-4EBE-93A6-386812DCA76D}">
-  <dimension ref="A1:Q307"/>
+  <dimension ref="A1:Q308"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="10.9375" bestFit="1" customWidth="1"/>
@@ -3653,6 +3673,9 @@
         <f t="shared" si="2"/>
         <v>1012</v>
       </c>
+      <c r="O14" t="s">
+        <v>693</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A15">
@@ -3764,7 +3787,7 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -4521,7 +4544,7 @@
         <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -8695,7 +8718,7 @@
         <v>181</v>
       </c>
       <c r="C169" t="s">
-        <v>10</v>
+        <v>327</v>
       </c>
       <c r="D169" t="s">
         <v>21</v>
@@ -8928,7 +8951,7 @@
         <v>189</v>
       </c>
       <c r="C176" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D176" t="s">
         <v>26</v>
@@ -9580,7 +9603,7 @@
         <v>210</v>
       </c>
       <c r="C196" t="s">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="D196" t="s">
         <v>26</v>
@@ -11761,7 +11784,7 @@
         <v/>
       </c>
       <c r="L261">
-        <f t="shared" ref="L261:L307" si="20">1000+A261</f>
+        <f t="shared" ref="L261:L308" si="20">1000+A261</f>
         <v>1259</v>
       </c>
     </row>
@@ -13194,6 +13217,30 @@
       <c r="L307">
         <f t="shared" si="20"/>
         <v>1305</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308" t="s">
+        <v>689</v>
+      </c>
+      <c r="C308" t="s">
+        <v>690</v>
+      </c>
+      <c r="D308" t="s">
+        <v>691</v>
+      </c>
+      <c r="E308" t="s">
+        <v>275</v>
+      </c>
+      <c r="F308" t="s">
+        <v>692</v>
+      </c>
+      <c r="L308">
+        <f t="shared" si="20"/>
+        <v>1306</v>
       </c>
     </row>
   </sheetData>
